--- a/artfynd/A 21611-2025 artfynd.xlsx
+++ b/artfynd/A 21611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2945,6 +2945,146 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128633715</v>
+      </c>
+      <c r="B19" t="n">
+        <v>30307</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100201</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Murvägstekel</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Agenioideus sericeus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Vander Linden, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>malaisefälla</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SIIP Trap ID 24, Holmön, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>790234</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7087652</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Holmön</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2018-07-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2018-07-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Primeval spruce forest</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Filip Adin</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Svenska InsektsInventeringsProjektet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21611-2025 artfynd.xlsx
+++ b/artfynd/A 21611-2025 artfynd.xlsx
@@ -2950,7 +2950,7 @@
         <v>128633715</v>
       </c>
       <c r="B19" t="n">
-        <v>30307</v>
+        <v>30309</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 21611-2025 artfynd.xlsx
+++ b/artfynd/A 21611-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3085,6 +3085,338 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129721479</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91607</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gersjöberget, Holmön, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>789442</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7087529</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Holmön</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129721480</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gersjöberget, Holmön, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>789555</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7087545</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Holmön</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129721478</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gersjöberget, Holmön, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>789469</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7087549</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Holmön</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21611-2025 artfynd.xlsx
+++ b/artfynd/A 21611-2025 artfynd.xlsx
@@ -3090,7 +3090,7 @@
         <v>129721479</v>
       </c>
       <c r="B20" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>129721480</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>129721478</v>
       </c>
       <c r="B22" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21611-2025 artfynd.xlsx
+++ b/artfynd/A 21611-2025 artfynd.xlsx
@@ -3090,7 +3090,7 @@
         <v>129721479</v>
       </c>
       <c r="B20" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>129721480</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>129721478</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21611-2025 artfynd.xlsx
+++ b/artfynd/A 21611-2025 artfynd.xlsx
@@ -3090,7 +3090,7 @@
         <v>129721479</v>
       </c>
       <c r="B20" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21611-2025 artfynd.xlsx
+++ b/artfynd/A 21611-2025 artfynd.xlsx
@@ -3090,7 +3090,7 @@
         <v>129721479</v>
       </c>
       <c r="B20" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 21611-2025 artfynd.xlsx
+++ b/artfynd/A 21611-2025 artfynd.xlsx
@@ -3090,7 +3090,7 @@
         <v>129721479</v>
       </c>
       <c r="B20" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>129721480</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>129721478</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21611-2025 artfynd.xlsx
+++ b/artfynd/A 21611-2025 artfynd.xlsx
@@ -3090,7 +3090,7 @@
         <v>129721479</v>
       </c>
       <c r="B20" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>129721480</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>129721478</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21611-2025 artfynd.xlsx
+++ b/artfynd/A 21611-2025 artfynd.xlsx
@@ -3090,7 +3090,7 @@
         <v>129721479</v>
       </c>
       <c r="B20" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>129721480</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>129721478</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 21611-2025 artfynd.xlsx
+++ b/artfynd/A 21611-2025 artfynd.xlsx
@@ -3090,7 +3090,7 @@
         <v>129721479</v>
       </c>
       <c r="B20" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>129721480</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>129721478</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
